--- a/investors_test_15_new.xlsx
+++ b/investors_test_15_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dantez\Downloads\ofds\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973170AC-0ADB-4107-920C-2A6EE343B1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF73BF88-CCDE-400D-875C-15E6792F29DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investors" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>investor_name</t>
   </si>
@@ -62,12 +62,6 @@
     <t>valuation</t>
   </si>
   <si>
-    <t>John Smith</t>
-  </si>
-  <si>
-    <t>AXIOM-001</t>
-  </si>
-  <si>
     <t>Axiom</t>
   </si>
   <si>
@@ -83,18 +77,31 @@
     <t>fund_name</t>
   </si>
   <si>
-    <t>emalarymond@gmail.com</t>
+    <t>Joy Kendi Muthuri</t>
+  </si>
+  <si>
+    <t>CN-002</t>
+  </si>
+  <si>
+    <t>Daniel Mungai</t>
+  </si>
+  <si>
+    <t>danielmungai900@gmail.com</t>
+  </si>
+  <si>
+    <t>kathonimary38@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,8 +134,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,6 +165,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,11 +198,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -197,8 +224,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -500,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -529,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -548,59 +579,75 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11">
+        <v>126184</v>
+      </c>
+      <c r="D3" s="12">
+        <v>10000</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="F3" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="11">
+        <v>166173</v>
+      </c>
+      <c r="D4" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -640,39 +687,28 @@
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{831579E9-2A1D-430A-B157-F11D8260BE50}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{D8616263-4EC9-4176-ACFD-725351AE5F6C}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{D9360C9F-3D7A-4C0C-A0AA-8FA13C9E59AA}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>